--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -32173,13 +32173,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R151" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -32332,10 +32332,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10054</v>
+        <v>10055</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -25135,13 +25135,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -25294,10 +25294,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -28525,13 +28525,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O134" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R134" t="n">
-        <v>0.283036132127281</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28684,10 +28684,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O135" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -32173,13 +32173,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R151" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -32332,10 +32332,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -32566,13 +32566,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32725,10 +32725,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10055</v>
+        <v>10069</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O132" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R132" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28291,10 +28291,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O133" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -32173,13 +32173,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R151" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -32332,10 +32332,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -32889,6 +32889,657 @@
       <c r="BC154" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>102</v>
+      </c>
+      <c r="O155" t="n">
+        <v>102</v>
+      </c>
+      <c r="P155" t="n">
+        <v>102</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0.02922338895424773</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>102</v>
+      </c>
+      <c r="O156" t="n">
+        <v>102</v>
+      </c>
+      <c r="P156" t="n">
+        <v>102</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>155</v>
+      </c>
+      <c r="O157" t="n">
+        <v>155</v>
+      </c>
+      <c r="P157" t="n">
+        <v>155</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32925,7 +33576,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -33008,7 +33659,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -33018,7 +33669,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -33038,7 +33689,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -33070,7 +33721,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10069</v>
+        <v>10174</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="O2" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="O3" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O23" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O24" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -12751,10 +12751,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O59" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O60" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -16531,10 +16531,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O77" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -16687,10 +16687,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O78" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -20962,10 +20962,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O98" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -21118,10 +21118,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O99" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -24703,12 +24703,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -24742,22 +24742,19 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="O116" t="n">
-        <v>21</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.3735499258814688</v>
+        <v>119</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -24777,12 +24774,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -24790,47 +24787,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24862,12 +24859,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -24901,24 +24898,24 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="O117" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -24933,7 +24930,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -24948,7 +24945,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -24983,17 +24980,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>PHO IDTO current-year monthly preliminary chronic hepatitis B notifications captured under the iPHIS carrier classification. Acute and chronic hepatitis B counts are not mutually exclusive when a case progresses to chronic infection.</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -25011,12 +25008,12 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -25024,47 +25021,47 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25096,12 +25093,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -25135,13 +25132,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O118" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -25150,7 +25147,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -25170,12 +25167,12 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -25183,47 +25180,47 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25255,12 +25252,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -25294,29 +25291,29 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O119" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -25341,7 +25338,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -25376,17 +25373,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25404,12 +25401,12 @@
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -25417,47 +25414,47 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25489,12 +25486,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -25519,7 +25516,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -25528,16 +25525,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="O120" t="n">
-        <v>63</v>
-      </c>
-      <c r="P120" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="R120" t="n">
-        <v>0.01804974023644713</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -25546,12 +25540,12 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -25561,7 +25555,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -25569,62 +25563,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25656,12 +25645,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -25686,7 +25675,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -25695,32 +25684,29 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="O121" t="n">
-        <v>63</v>
-      </c>
-      <c r="P121" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -25730,12 +25716,12 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -25745,7 +25731,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -25760,7 +25746,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
@@ -25780,17 +25766,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25803,7 +25789,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -25811,62 +25797,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25893,7 +25874,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -25937,106 +25918,31 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>149</v>
+        <v>63</v>
       </c>
       <c r="O122" t="n">
-        <v>149</v>
+        <v>63</v>
       </c>
       <c r="P122" t="n">
-        <v>149</v>
+        <v>63</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.01804974023644713</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>0</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -26135,7 +26041,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -26170,7 +26076,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -26179,31 +26085,106 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="O123" t="n">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="P123" t="n">
-        <v>119</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.03409395377995569</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -26337,7 +26318,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -26346,22 +26327,22 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="O124" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="P124" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -26371,7 +26352,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -26436,7 +26417,7 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -26445,7 +26426,7 @@
         </is>
       </c>
       <c r="AN124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -26544,7 +26525,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -26588,106 +26569,31 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="O125" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="P125" t="n">
-        <v>183</v>
+        <v>119</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.03409395377995569</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>0</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -26786,7 +26692,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -26821,7 +26727,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -26830,31 +26736,106 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="O126" t="n">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="P126" t="n">
-        <v>227</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0.06503636561386504</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>119</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -26988,7 +26969,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -26997,22 +26978,22 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="O127" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="P127" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -27022,7 +27003,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -27087,7 +27068,7 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -27096,7 +27077,7 @@
         </is>
       </c>
       <c r="AN127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -27195,7 +27176,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -27239,106 +27220,31 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="O128" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="P128" t="n">
-        <v>241</v>
+        <v>227</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.06503636561386504</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>0</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -27437,7 +27343,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -27472,7 +27378,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -27481,31 +27387,106 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>125</v>
+        <v>227</v>
       </c>
       <c r="O129" t="n">
-        <v>125</v>
+        <v>227</v>
       </c>
       <c r="P129" t="n">
-        <v>125</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.03581297665961732</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>227</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -27639,7 +27620,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -27648,22 +27629,22 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="O130" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="P130" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
@@ -27673,7 +27654,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -27738,7 +27719,7 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -27747,7 +27728,7 @@
         </is>
       </c>
       <c r="AN130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -27846,7 +27827,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -27890,106 +27871,31 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="O131" t="n">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="P131" t="n">
-        <v>183</v>
+        <v>125</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.03581297665961732</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>0</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -28088,17 +27994,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -28123,37 +28029,115 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="O132" t="n">
-        <v>17</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0.3023975590469034</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="P132" t="n">
+        <v>125</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -28162,65 +28146,70 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28252,12 +28241,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -28282,38 +28271,41 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="O133" t="n">
-        <v>17</v>
+        <v>183</v>
+      </c>
+      <c r="P133" t="n">
+        <v>183</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -28323,12 +28315,12 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
@@ -28338,7 +28330,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -28353,7 +28345,7 @@
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG133" t="inlineStr">
@@ -28373,21 +28365,21 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -28396,65 +28388,70 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28486,12 +28483,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -28525,13 +28522,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O134" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R134" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28540,7 +28537,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -28560,12 +28557,12 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -28573,47 +28570,47 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28645,12 +28642,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -28684,29 +28681,29 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O135" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -28731,7 +28728,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -28766,17 +28763,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28794,12 +28791,12 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -28807,47 +28804,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28879,12 +28876,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -28918,16 +28915,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="O136" t="n">
-        <v>152</v>
-      </c>
-      <c r="P136" t="n">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="R136" t="n">
-        <v>0.04354857961809466</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -28936,12 +28930,12 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -28951,7 +28945,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -28959,62 +28953,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29046,12 +29035,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -29085,32 +29074,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="O137" t="n">
-        <v>152</v>
-      </c>
-      <c r="P137" t="n">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -29120,12 +29106,12 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
@@ -29135,7 +29121,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -29150,7 +29136,7 @@
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
@@ -29170,17 +29156,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -29193,7 +29179,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -29201,62 +29187,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29283,7 +29264,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -29327,106 +29308,31 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="O138" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="P138" t="n">
-        <v>231</v>
+        <v>152</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.04354857961809466</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>0</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -29525,7 +29431,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -29560,7 +29466,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -29569,31 +29475,106 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="O139" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="P139" t="n">
-        <v>108</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.03094241183390936</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -29727,7 +29708,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -29736,22 +29717,22 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="O140" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="P140" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -29761,7 +29742,7 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
@@ -29826,7 +29807,7 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -29835,7 +29816,7 @@
         </is>
       </c>
       <c r="AN140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -29934,7 +29915,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -29978,106 +29959,31 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="O141" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="P141" t="n">
-        <v>203</v>
+        <v>108</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.03094241183390936</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>0</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -30176,7 +30082,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -30211,7 +30117,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -30220,31 +30126,106 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O142" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P142" t="n">
-        <v>111</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.03180192327374018</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>108</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -30378,7 +30359,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -30387,22 +30368,22 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="O143" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="P143" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
@@ -30412,7 +30393,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -30477,7 +30458,7 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -30486,7 +30467,7 @@
         </is>
       </c>
       <c r="AN143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -30585,7 +30566,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -30629,106 +30610,31 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
       <c r="O144" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
       <c r="P144" t="n">
-        <v>209</v>
+        <v>111</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.03180192327374018</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>0</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -30827,7 +30733,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -30862,7 +30768,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -30871,31 +30777,106 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="O145" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="P145" t="n">
-        <v>222</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.06360384654748036</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>111</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -31029,7 +31010,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -31038,22 +31019,22 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="O146" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="P146" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -31063,7 +31044,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -31128,7 +31109,7 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -31137,7 +31118,7 @@
         </is>
       </c>
       <c r="AN146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -31236,7 +31217,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -31280,106 +31261,31 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="O147" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="P147" t="n">
-        <v>199</v>
+        <v>222</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.06360384654748036</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>0</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -31478,7 +31384,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -31513,7 +31419,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -31522,31 +31428,106 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="O148" t="n">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="P148" t="n">
-        <v>95</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.02721786226130916</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>222</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -31680,7 +31661,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -31689,22 +31670,22 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="O149" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="P149" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -31714,7 +31695,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -31779,7 +31760,7 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
@@ -31788,7 +31769,7 @@
         </is>
       </c>
       <c r="AN149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -31887,7 +31868,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -31931,106 +31912,31 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="O150" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="P150" t="n">
-        <v>173</v>
+        <v>95</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.02721786226130916</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>0</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -32129,17 +32035,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -32164,37 +32070,115 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0.08894045854320688</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>95</v>
+      </c>
+      <c r="P151" t="n">
+        <v>95</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -32203,65 +32187,70 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32293,12 +32282,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -32323,38 +32312,41 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>173</v>
+      </c>
+      <c r="P152" t="n">
+        <v>173</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -32364,12 +32356,12 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
@@ -32379,7 +32371,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -32394,7 +32386,7 @@
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
@@ -32414,21 +32406,21 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -32437,65 +32429,70 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32527,12 +32524,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -32566,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32581,7 +32578,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -32601,12 +32598,12 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -32614,47 +32611,47 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32686,12 +32683,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -32725,29 +32722,29 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -32772,7 +32769,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -32807,17 +32804,17 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -32835,12 +32832,12 @@
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT154" t="n">
@@ -32848,47 +32845,47 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32920,12 +32917,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -32950,7 +32947,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -32959,16 +32956,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="O155" t="n">
-        <v>102</v>
-      </c>
-      <c r="P155" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="R155" t="n">
-        <v>0.02922338895424773</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -32977,12 +32971,12 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -32992,7 +32986,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -33000,62 +32994,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33087,12 +33076,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -33117,7 +33106,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -33126,32 +33115,29 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="O156" t="n">
-        <v>102</v>
-      </c>
-      <c r="P156" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -33161,12 +33147,12 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
@@ -33176,7 +33162,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -33191,7 +33177,7 @@
       </c>
       <c r="AF156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG156" t="inlineStr">
@@ -33211,17 +33197,17 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -33234,7 +33220,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -33242,62 +33228,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33324,7 +33305,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -33368,106 +33349,31 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="O157" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="P157" t="n">
-        <v>155</v>
+        <v>102</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.02922338895424773</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>0</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -33538,6 +33444,490 @@
         </is>
       </c>
       <c r="BC157" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>102</v>
+      </c>
+      <c r="O158" t="n">
+        <v>102</v>
+      </c>
+      <c r="P158" t="n">
+        <v>102</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>155</v>
+      </c>
+      <c r="O159" t="n">
+        <v>155</v>
+      </c>
+      <c r="P159" t="n">
+        <v>155</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -33659,7 +34049,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -33669,7 +34059,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -33689,7 +34079,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -33721,7 +34111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10174</v>
+        <v>10315</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -32563,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O153" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R153" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32722,10 +32722,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10315</v>
+        <v>10317</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -32563,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32722,10 +32722,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10317</v>
+        <v>10320</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -28915,13 +28915,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R136" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.3361054069011462</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -29074,10 +29074,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O137" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -32956,13 +32956,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="O155" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.3361054069011462</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -33115,10 +33115,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="O156" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10320</v>
+        <v>10330</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -25132,13 +25132,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O118" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R118" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -25291,10 +25291,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -32563,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32722,10 +32722,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -33933,6 +33933,657 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>84</v>
+      </c>
+      <c r="O160" t="n">
+        <v>84</v>
+      </c>
+      <c r="P160" t="n">
+        <v>84</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.02406632031526284</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>84</v>
+      </c>
+      <c r="O161" t="n">
+        <v>84</v>
+      </c>
+      <c r="P161" t="n">
+        <v>84</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>184</v>
+      </c>
+      <c r="O162" t="n">
+        <v>184</v>
+      </c>
+      <c r="P162" t="n">
+        <v>184</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33966,7 +34617,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -34049,7 +34700,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -34059,7 +34710,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -34079,7 +34730,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -34111,7 +34762,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10330</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -26170,7 +26170,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26821,7 +26821,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27063,7 +27063,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28522,13 +28522,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O134" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R134" t="n">
-        <v>0.3023975590469034</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28681,10 +28681,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29802,7 +29802,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30453,7 +30453,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31755,7 +31755,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32406,7 +32406,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -32563,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O153" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32722,10 +32722,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O154" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -32956,13 +32956,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O155" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3361054069011462</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -33115,10 +33115,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O156" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -33843,7 +33843,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34494,7 +34494,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -34579,6 +34579,657 @@
         </is>
       </c>
       <c r="BC162" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>142</v>
+      </c>
+      <c r="O163" t="n">
+        <v>142</v>
+      </c>
+      <c r="P163" t="n">
+        <v>142</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.04068354148532527</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>142</v>
+      </c>
+      <c r="O164" t="n">
+        <v>142</v>
+      </c>
+      <c r="P164" t="n">
+        <v>142</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>211</v>
+      </c>
+      <c r="O165" t="n">
+        <v>211</v>
+      </c>
+      <c r="P165" t="n">
+        <v>211</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -34617,7 +35268,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -34700,7 +35351,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -34710,7 +35361,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -34730,7 +35381,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -34762,7 +35413,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10414</v>
+        <v>10569</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -32563,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O153" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R153" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32722,10 +32722,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O154" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -35232,6 +35232,1050 @@
       <c r="BC165" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>112</v>
+      </c>
+      <c r="O166" t="n">
+        <v>112</v>
+      </c>
+      <c r="P166" t="n">
+        <v>112</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.03208842708701712</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>112</v>
+      </c>
+      <c r="O167" t="n">
+        <v>112</v>
+      </c>
+      <c r="P167" t="n">
+        <v>112</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>195</v>
+      </c>
+      <c r="O168" t="n">
+        <v>195</v>
+      </c>
+      <c r="P168" t="n">
+        <v>195</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35268,7 +36312,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -35351,7 +36395,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -35361,7 +36405,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -35381,7 +36425,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -35413,7 +36457,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10569</v>
+        <v>10689</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -28915,13 +28915,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O136" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R136" t="n">
-        <v>0.3361054069011462</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -29074,10 +29074,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O137" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -32563,13 +32563,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O153" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R153" t="n">
-        <v>0.5158546595505998</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -32722,10 +32722,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O154" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -32956,13 +32956,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O155" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.4422439564488765</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -33115,10 +33115,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O156" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -35953,13 +35953,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -36112,10 +36112,10 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10689</v>
+        <v>10697</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O23" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O24" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -8971,10 +8971,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O41" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O42" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -12751,10 +12751,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O59" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O60" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -16531,10 +16531,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O77" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -16687,10 +16687,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O78" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -20962,10 +20962,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O98" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -21118,10 +21118,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O99" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -24742,10 +24742,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O116" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -24898,10 +24898,10 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O117" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -28483,12 +28483,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -28522,22 +28522,19 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="O134" t="n">
-        <v>18</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0.3201856507555447</v>
+        <v>101</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -28557,12 +28554,12 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -28570,47 +28567,47 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28642,12 +28639,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -28681,24 +28678,24 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="O135" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -28713,7 +28710,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -28728,7 +28725,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -28763,17 +28760,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>PHO IDTO current-year monthly preliminary chronic hepatitis B notifications captured under the iPHIS carrier classification. Acute and chronic hepatitis B counts are not mutually exclusive when a case progresses to chronic infection.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28791,12 +28788,12 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -28804,47 +28801,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28876,12 +28873,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -28915,13 +28912,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O136" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R136" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -28930,7 +28927,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -28950,12 +28947,12 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -28963,47 +28960,47 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29035,12 +29032,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -29074,29 +29071,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O137" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -29121,7 +29118,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -29156,17 +29153,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -29184,12 +29181,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -29197,47 +29194,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29269,12 +29266,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -29308,16 +29305,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="O138" t="n">
-        <v>152</v>
-      </c>
-      <c r="P138" t="n">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="R138" t="n">
-        <v>0.04354857961809466</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -29326,12 +29320,12 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -29341,7 +29335,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -29349,62 +29343,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29436,12 +29425,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -29475,32 +29464,29 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="O139" t="n">
-        <v>152</v>
-      </c>
-      <c r="P139" t="n">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -29510,12 +29496,12 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
@@ -29525,7 +29511,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -29540,7 +29526,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG139" t="inlineStr">
@@ -29560,17 +29546,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29583,7 +29569,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -29591,62 +29577,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29673,7 +29654,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -29717,106 +29698,31 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="O140" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="P140" t="n">
-        <v>231</v>
+        <v>152</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.04354857961809466</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>0</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -29915,7 +29821,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -29950,7 +29856,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -29959,31 +29865,106 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="O141" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="P141" t="n">
-        <v>108</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.03094241183390936</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -30117,7 +30098,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -30126,22 +30107,22 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="O142" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="P142" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -30151,7 +30132,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -30216,7 +30197,7 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -30225,7 +30206,7 @@
         </is>
       </c>
       <c r="AN142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -30324,7 +30305,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -30368,106 +30349,31 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="O143" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="P143" t="n">
-        <v>203</v>
+        <v>108</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.03094241183390936</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>0</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -30566,7 +30472,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -30601,7 +30507,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -30610,31 +30516,106 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O144" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P144" t="n">
-        <v>111</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.03180192327374018</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>108</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -30768,7 +30749,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -30777,22 +30758,22 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="O145" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="P145" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -30802,7 +30783,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -30867,7 +30848,7 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -30876,7 +30857,7 @@
         </is>
       </c>
       <c r="AN145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -30975,7 +30956,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -31019,106 +31000,31 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
       <c r="O146" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
       <c r="P146" t="n">
-        <v>209</v>
+        <v>111</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.03180192327374018</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
-        <v>0</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -31217,7 +31123,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -31252,7 +31158,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -31261,31 +31167,106 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="O147" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="P147" t="n">
-        <v>222</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0.06360384654748036</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>111</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -31419,7 +31400,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -31428,22 +31409,22 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="O148" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="P148" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -31453,7 +31434,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -31518,7 +31499,7 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -31527,7 +31508,7 @@
         </is>
       </c>
       <c r="AN148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -31626,7 +31607,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -31670,106 +31651,31 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="O149" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="P149" t="n">
-        <v>199</v>
+        <v>222</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.06360384654748036</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>0</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
@@ -31868,7 +31774,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -31903,7 +31809,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -31912,31 +31818,106 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="O150" t="n">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="P150" t="n">
-        <v>95</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0.02721786226130916</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>222</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -32070,7 +32051,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -32079,22 +32060,22 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="O151" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="P151" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -32104,7 +32085,7 @@
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -32169,7 +32150,7 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -32178,7 +32159,7 @@
         </is>
       </c>
       <c r="AN151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -32277,7 +32258,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -32321,106 +32302,31 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="O152" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="P152" t="n">
-        <v>173</v>
+        <v>95</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.02721786226130916</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>0</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -32519,17 +32425,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -32554,37 +32460,115 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="O153" t="n">
-        <v>30</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0.5336427512592412</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>95</v>
+      </c>
+      <c r="P153" t="n">
+        <v>95</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -32593,65 +32577,70 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32683,12 +32672,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -32713,38 +32702,41 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="O154" t="n">
-        <v>30</v>
+        <v>173</v>
+      </c>
+      <c r="P154" t="n">
+        <v>173</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -32754,12 +32746,12 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
@@ -32769,7 +32761,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -32784,7 +32776,7 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG154" t="inlineStr">
@@ -32804,21 +32796,21 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -32827,65 +32819,70 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32917,12 +32914,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -32956,13 +32953,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O155" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R155" t="n">
-        <v>0.4422439564488765</v>
+        <v>0.569218934676524</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -32971,7 +32968,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -32991,12 +32988,12 @@
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -33004,47 +33001,47 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33076,12 +33073,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -33115,29 +33112,29 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O156" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -33162,7 +33159,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -33197,17 +33194,17 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -33225,12 +33222,12 @@
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -33238,47 +33235,47 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33310,12 +33307,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -33340,7 +33337,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -33349,16 +33346,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="O157" t="n">
-        <v>102</v>
-      </c>
-      <c r="P157" t="n">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="R157" t="n">
-        <v>0.02922338895424773</v>
+        <v>0.4776234729647867</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -33367,12 +33361,12 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -33382,7 +33376,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -33390,62 +33384,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33477,12 +33466,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -33507,7 +33496,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -33516,32 +33505,29 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="O158" t="n">
-        <v>102</v>
-      </c>
-      <c r="P158" t="n">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
@@ -33551,12 +33537,12 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
@@ -33566,7 +33552,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -33581,7 +33567,7 @@
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG158" t="inlineStr">
@@ -33601,17 +33587,17 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -33624,7 +33610,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -33632,62 +33618,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33714,7 +33695,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -33758,106 +33739,31 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="O159" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="P159" t="n">
-        <v>155</v>
+        <v>102</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.02922338895424773</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>0</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -33956,7 +33862,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -33991,7 +33897,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -34000,31 +33906,106 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="O160" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="P160" t="n">
-        <v>84</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0.02406632031526284</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>102</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
@@ -34158,7 +34139,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -34167,22 +34148,22 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="O161" t="n">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="P161" t="n">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -34192,7 +34173,7 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -34257,7 +34238,7 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -34266,7 +34247,7 @@
         </is>
       </c>
       <c r="AN161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -34365,7 +34346,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -34409,106 +34390,31 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="O162" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="P162" t="n">
-        <v>184</v>
+        <v>84</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.02406632031526284</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>0</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -34607,7 +34513,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -34642,7 +34548,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -34651,31 +34557,106 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="O163" t="n">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="P163" t="n">
-        <v>142</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.04068354148532527</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>84</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
@@ -34809,7 +34790,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -34818,22 +34799,22 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="O164" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="P164" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
@@ -34843,7 +34824,7 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
@@ -34908,7 +34889,7 @@
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
@@ -34917,7 +34898,7 @@
         </is>
       </c>
       <c r="AN164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -35016,7 +34997,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -35060,106 +35041,31 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="O165" t="n">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="P165" t="n">
-        <v>211</v>
+        <v>142</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.04068354148532527</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>0</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -35258,7 +35164,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -35293,7 +35199,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -35302,31 +35208,106 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="O166" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="P166" t="n">
-        <v>112</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0.03208842708701712</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>142</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -35460,7 +35441,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -35469,22 +35450,22 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="O167" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="P167" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
@@ -35494,7 +35475,7 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -35559,7 +35540,7 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -35568,7 +35549,7 @@
         </is>
       </c>
       <c r="AN167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
@@ -35667,7 +35648,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -35711,106 +35692,31 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="O168" t="n">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="P168" t="n">
-        <v>195</v>
+        <v>112</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.03208842708701712</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>0</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -35909,17 +35815,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -35944,38 +35850,116 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N169" t="n">
+        <v>112</v>
+      </c>
+      <c r="O169" t="n">
+        <v>112</v>
+      </c>
+      <c r="P169" t="n">
+        <v>112</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
         <v>1</v>
       </c>
-      <c r="O169" t="n">
-        <v>1</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_141</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35983,65 +35967,70 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36073,209 +36062,1654 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>195</v>
+      </c>
+      <c r="O170" t="n">
+        <v>195</v>
+      </c>
+      <c r="P170" t="n">
+        <v>195</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H171" t="inlineStr">
         <is>
           <t>D208</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t>Chronic hepatitis B</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="J171" t="inlineStr">
         <is>
           <t>慢性乙型肝炎</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="K171" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N170" t="n">
+      <c r="N171" t="n">
+        <v>7</v>
+      </c>
+      <c r="O171" t="n">
+        <v>7</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
         <v>1</v>
       </c>
-      <c r="O170" t="n">
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>7</v>
+      </c>
+      <c r="O172" t="n">
+        <v>7</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
         <v>1</v>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_141</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
+      <c r="AT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="n">
+        <v>1</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="n">
+        <v>1</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Hepatitt B, kronisk</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
+      <c r="Z174" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA170" t="inlineStr">
+      <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
+      <c r="AB174" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE170" t="inlineStr">
+      <c r="AE174" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF170" t="inlineStr">
+      <c r="AF174" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG170" t="inlineStr">
+      <c r="AG174" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH170" t="inlineStr">
+      <c r="AH174" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI170" t="inlineStr">
+      <c r="AI174" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN174" t="b">
         <v>1</v>
       </c>
-      <c r="AO170" t="inlineStr">
+      <c r="AO174" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP170" t="inlineStr">
+      <c r="AP174" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_141</t>
-        </is>
-      </c>
-      <c r="AT170" t="n">
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT174" t="n">
         <v>1</v>
       </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV170" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
-      <c r="AW170" t="inlineStr">
-        <is>
-          <t>Finland THL Infectious Diseases Register</t>
-        </is>
-      </c>
-      <c r="AX170" t="inlineStr">
-        <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr">
-        <is>
-          <t>cube_csv</t>
-        </is>
-      </c>
-      <c r="AZ170" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
-      <c r="BA170" t="inlineStr">
-        <is>
-          <t>Finland THL Infectious Diseases Register</t>
-        </is>
-      </c>
-      <c r="BB170" t="inlineStr">
-        <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
-        </is>
-      </c>
-      <c r="BC170" t="inlineStr">
-        <is>
-          <t>cube_csv</t>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>140</v>
+      </c>
+      <c r="O175" t="n">
+        <v>140</v>
+      </c>
+      <c r="P175" t="n">
+        <v>140</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.0401105338587714</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>140</v>
+      </c>
+      <c r="O176" t="n">
+        <v>140</v>
+      </c>
+      <c r="P176" t="n">
+        <v>140</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>275</v>
+      </c>
+      <c r="O177" t="n">
+        <v>275</v>
+      </c>
+      <c r="P177" t="n">
+        <v>275</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36312,7 +37746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -36395,7 +37829,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -36405,7 +37839,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -36425,7 +37859,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -36457,7 +37891,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10697</v>
+        <v>10954</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -36343,13 +36343,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R171" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -36502,10 +36502,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10954</v>
+        <v>10955</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -29305,13 +29305,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R138" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.3891746816750113</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -29464,10 +29464,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O139" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -32953,13 +32953,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O155" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R155" t="n">
-        <v>0.569218934676524</v>
+        <v>0.5870070263851653</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -33112,10 +33112,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O156" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -36343,13 +36343,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O171" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R171" t="n">
-        <v>0.142304733669131</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -36502,10 +36502,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O172" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -36736,13 +36736,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O173" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R173" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -36895,10 +36895,10 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10955</v>
+        <v>10964</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -37713,6 +37713,657 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>129</v>
+      </c>
+      <c r="O178" t="n">
+        <v>129</v>
+      </c>
+      <c r="P178" t="n">
+        <v>129</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.03695899191272507</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>129</v>
+      </c>
+      <c r="O179" t="n">
+        <v>129</v>
+      </c>
+      <c r="P179" t="n">
+        <v>129</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>201</v>
+      </c>
+      <c r="O180" t="n">
+        <v>201</v>
+      </c>
+      <c r="P180" t="n">
+        <v>201</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37746,7 +38397,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -37829,7 +38480,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -37839,7 +38490,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -37859,7 +38510,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -37891,7 +38542,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10964</v>
+        <v>11093</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -9370,13 +9370,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O61" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R61" t="n">
-        <v>0.6047951180938068</v>
+        <v>0.6225832098024481</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R67" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11098</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -1185,14 +1185,12 @@
       <c r="O5" t="n">
         <v>34</v>
       </c>
+      <c r="P5" t="n">
+        <v>34</v>
+      </c>
       <c r="R5" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1205,23 +1203,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1335,14 +1323,12 @@
       <c r="O6" t="n">
         <v>210</v>
       </c>
+      <c r="P6" t="n">
+        <v>210</v>
+      </c>
       <c r="R6" t="n">
         <v>0.06016580078815709</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1355,23 +1341,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1485,14 +1461,12 @@
       <c r="O7" t="n">
         <v>228</v>
       </c>
+      <c r="P7" t="n">
+        <v>228</v>
+      </c>
       <c r="R7" t="n">
         <v>0.06532286942714199</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1505,23 +1479,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1635,14 +1599,12 @@
       <c r="O8" t="n">
         <v>103</v>
       </c>
+      <c r="P8" t="n">
+        <v>103</v>
+      </c>
       <c r="R8" t="n">
         <v>0.02950989276752467</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1655,23 +1617,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1785,14 +1737,12 @@
       <c r="O9" t="n">
         <v>92</v>
       </c>
+      <c r="P9" t="n">
+        <v>92</v>
+      </c>
       <c r="R9" t="n">
         <v>0.02635835082147835</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1805,23 +1755,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2355,14 +2295,12 @@
       <c r="O13" t="n">
         <v>315</v>
       </c>
+      <c r="P13" t="n">
+        <v>315</v>
+      </c>
       <c r="R13" t="n">
         <v>0.09024870118223564</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2375,23 +2313,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2505,14 +2433,12 @@
       <c r="O14" t="n">
         <v>86</v>
       </c>
+      <c r="P14" t="n">
+        <v>86</v>
+      </c>
       <c r="R14" t="n">
         <v>0.02463932794181671</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2525,23 +2451,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2655,14 +2571,12 @@
       <c r="O15" t="n">
         <v>196</v>
       </c>
+      <c r="P15" t="n">
+        <v>196</v>
+      </c>
       <c r="R15" t="n">
         <v>0.05615474740227996</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2675,23 +2589,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2805,14 +2709,12 @@
       <c r="O16" t="n">
         <v>98</v>
       </c>
+      <c r="P16" t="n">
+        <v>98</v>
+      </c>
       <c r="R16" t="n">
         <v>0.02807737370113998</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2825,23 +2727,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3375,14 +3267,12 @@
       <c r="O20" t="n">
         <v>116</v>
       </c>
+      <c r="P20" t="n">
+        <v>116</v>
+      </c>
       <c r="R20" t="n">
         <v>0.03323444234012487</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3395,23 +3285,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3525,14 +3405,12 @@
       <c r="O21" t="n">
         <v>181</v>
       </c>
+      <c r="P21" t="n">
+        <v>181</v>
+      </c>
       <c r="R21" t="n">
         <v>0.05185719020312587</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3545,23 +3423,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3675,14 +3543,12 @@
       <c r="O22" t="n">
         <v>117</v>
       </c>
+      <c r="P22" t="n">
+        <v>117</v>
+      </c>
       <c r="R22" t="n">
         <v>0.03352094615340181</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3695,23 +3561,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3825,14 +3681,12 @@
       <c r="O23" t="n">
         <v>136</v>
       </c>
+      <c r="P23" t="n">
+        <v>136</v>
+      </c>
       <c r="R23" t="n">
         <v>0.03896451860566364</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3845,23 +3699,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4395,14 +4239,12 @@
       <c r="O27" t="n">
         <v>129</v>
       </c>
+      <c r="P27" t="n">
+        <v>129</v>
+      </c>
       <c r="R27" t="n">
         <v>0.03695899191272507</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4415,23 +4257,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4545,14 +4377,12 @@
       <c r="O28" t="n">
         <v>134</v>
       </c>
+      <c r="P28" t="n">
+        <v>134</v>
+      </c>
       <c r="R28" t="n">
         <v>0.03839151097910976</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4565,23 +4395,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4695,14 +4515,12 @@
       <c r="O29" t="n">
         <v>128</v>
       </c>
+      <c r="P29" t="n">
+        <v>128</v>
+      </c>
       <c r="R29" t="n">
         <v>0.03667248809944813</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4715,23 +4533,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4845,14 +4653,12 @@
       <c r="O30" t="n">
         <v>4019</v>
       </c>
+      <c r="P30" t="n">
+        <v>4019</v>
+      </c>
       <c r="R30" t="n">
         <v>1.151458825560016</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4865,23 +4671,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5415,14 +5211,12 @@
       <c r="O34" t="n">
         <v>142</v>
       </c>
+      <c r="P34" t="n">
+        <v>142</v>
+      </c>
       <c r="R34" t="n">
         <v>0.04068354148532527</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5435,23 +5229,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5565,14 +5349,12 @@
       <c r="O35" t="n">
         <v>129</v>
       </c>
+      <c r="P35" t="n">
+        <v>129</v>
+      </c>
       <c r="R35" t="n">
         <v>0.03695899191272507</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5585,23 +5367,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5715,14 +5487,12 @@
       <c r="O36" t="n">
         <v>366</v>
       </c>
+      <c r="P36" t="n">
+        <v>366</v>
+      </c>
       <c r="R36" t="n">
         <v>0.1048603956593595</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5735,23 +5505,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5865,14 +5625,12 @@
       <c r="O37" t="n">
         <v>57</v>
       </c>
+      <c r="P37" t="n">
+        <v>57</v>
+      </c>
       <c r="R37" t="n">
         <v>0.0163307173567855</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5885,23 +5643,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6015,14 +5763,12 @@
       <c r="O38" t="n">
         <v>86</v>
       </c>
+      <c r="P38" t="n">
+        <v>86</v>
+      </c>
       <c r="R38" t="n">
         <v>0.02463932794181671</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6035,23 +5781,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6585,14 +6321,12 @@
       <c r="O42" t="n">
         <v>255</v>
       </c>
+      <c r="P42" t="n">
+        <v>255</v>
+      </c>
       <c r="R42" t="n">
         <v>0.07305847238561933</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6605,23 +6339,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6735,14 +6459,12 @@
       <c r="O43" t="n">
         <v>114</v>
       </c>
+      <c r="P43" t="n">
+        <v>114</v>
+      </c>
       <c r="R43" t="n">
         <v>0.032661434713571</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6755,23 +6477,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6885,14 +6597,12 @@
       <c r="O44" t="n">
         <v>158</v>
       </c>
+      <c r="P44" t="n">
+        <v>158</v>
+      </c>
       <c r="R44" t="n">
         <v>0.04526760249775628</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6905,23 +6615,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7035,14 +6735,12 @@
       <c r="O45" t="n">
         <v>111</v>
       </c>
+      <c r="P45" t="n">
+        <v>111</v>
+      </c>
       <c r="R45" t="n">
         <v>0.03180192327374018</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7055,23 +6753,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7605,14 +7293,12 @@
       <c r="O49" t="n">
         <v>63</v>
       </c>
+      <c r="P49" t="n">
+        <v>63</v>
+      </c>
       <c r="R49" t="n">
         <v>0.01804974023644713</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7625,23 +7311,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7755,14 +7431,12 @@
       <c r="O50" t="n">
         <v>119</v>
       </c>
+      <c r="P50" t="n">
+        <v>119</v>
+      </c>
       <c r="R50" t="n">
         <v>0.03409395377995569</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7775,23 +7449,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7905,14 +7569,12 @@
       <c r="O51" t="n">
         <v>227</v>
       </c>
+      <c r="P51" t="n">
+        <v>227</v>
+      </c>
       <c r="R51" t="n">
         <v>0.06503636561386504</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7925,23 +7587,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8055,14 +7707,12 @@
       <c r="O52" t="n">
         <v>125</v>
       </c>
+      <c r="P52" t="n">
+        <v>125</v>
+      </c>
       <c r="R52" t="n">
         <v>0.03581297665961732</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8075,23 +7725,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8625,14 +8265,12 @@
       <c r="O56" t="n">
         <v>152</v>
       </c>
+      <c r="P56" t="n">
+        <v>152</v>
+      </c>
       <c r="R56" t="n">
         <v>0.04354857961809466</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8645,23 +8283,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8775,14 +8403,12 @@
       <c r="O57" t="n">
         <v>108</v>
       </c>
+      <c r="P57" t="n">
+        <v>108</v>
+      </c>
       <c r="R57" t="n">
         <v>0.03094241183390936</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8795,23 +8421,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8925,14 +8541,12 @@
       <c r="O58" t="n">
         <v>111</v>
       </c>
+      <c r="P58" t="n">
+        <v>111</v>
+      </c>
       <c r="R58" t="n">
         <v>0.03180192327374018</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8945,23 +8559,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9075,14 +8679,12 @@
       <c r="O59" t="n">
         <v>222</v>
       </c>
+      <c r="P59" t="n">
+        <v>222</v>
+      </c>
       <c r="R59" t="n">
         <v>0.06360384654748036</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9095,23 +8697,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9225,14 +8817,12 @@
       <c r="O60" t="n">
         <v>95</v>
       </c>
+      <c r="P60" t="n">
+        <v>95</v>
+      </c>
       <c r="R60" t="n">
         <v>0.02721786226130916</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9245,23 +8835,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9663,14 +9243,12 @@
       <c r="O63" t="n">
         <v>102</v>
       </c>
+      <c r="P63" t="n">
+        <v>102</v>
+      </c>
       <c r="R63" t="n">
         <v>0.02922338895424773</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9683,23 +9261,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9813,14 +9381,12 @@
       <c r="O64" t="n">
         <v>84</v>
       </c>
+      <c r="P64" t="n">
+        <v>84</v>
+      </c>
       <c r="R64" t="n">
         <v>0.02406632031526284</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9833,23 +9399,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9963,14 +9519,12 @@
       <c r="O65" t="n">
         <v>142</v>
       </c>
+      <c r="P65" t="n">
+        <v>142</v>
+      </c>
       <c r="R65" t="n">
         <v>0.04068354148532527</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9983,23 +9537,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10113,14 +9657,12 @@
       <c r="O66" t="n">
         <v>112</v>
       </c>
+      <c r="P66" t="n">
+        <v>112</v>
+      </c>
       <c r="R66" t="n">
         <v>0.03208842708701712</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10133,23 +9675,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10402,13 +9934,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10551,14 +10083,12 @@
       <c r="O69" t="n">
         <v>140</v>
       </c>
+      <c r="P69" t="n">
+        <v>140</v>
+      </c>
       <c r="R69" t="n">
         <v>0.0401105338587714</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10571,23 +10101,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10701,14 +10221,12 @@
       <c r="O70" t="n">
         <v>129</v>
       </c>
+      <c r="P70" t="n">
+        <v>129</v>
+      </c>
       <c r="R70" t="n">
         <v>0.03695899191272507</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10721,23 +10239,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10774,6 +10282,144 @@
         </is>
       </c>
       <c r="BC70" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>116</v>
+      </c>
+      <c r="O71" t="n">
+        <v>116</v>
+      </c>
+      <c r="P71" t="n">
+        <v>116</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.03323444234012487</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -10812,7 +10458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10541,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10905,7 +10551,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -10957,7 +10603,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11100</v>
+        <v>11217</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -9790,13 +9790,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R67" t="n">
-        <v>0.3023975590469034</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11217</v>
+        <v>11218</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -9790,13 +9790,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O67" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R67" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11218</v>
+        <v>11222</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -14392,13 +14392,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O85" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R85" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.4980665678419585</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O86" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11226</v>
+        <v>11232</v>
       </c>
     </row>
     <row r="16">
